--- a/tests/fixtures/formula_storage/split_clear.xlsx
+++ b/tests/fixtures/formula_storage/split_clear.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\formula_storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B39AEAB-573C-40CE-BA02-520AD37C6ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5EF8507-0F59-4DE1-8676-75A1B8F27EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="7200" windowHeight="4425" xr2:uid="{411970AC-06D8-4752-B58C-FA2EC87F9F26}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="7200" windowHeight="4425" xr2:uid="{C823F5A8-5044-4511-9B4E-38A6B470BD49}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF53AB8-5E31-49D3-A732-092467E32A4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0956B4-CF41-4513-B340-A13965293961}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/tests/fixtures/formula_storage/split_clear.xlsx
+++ b/tests/fixtures/formula_storage/split_clear.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\formula_storage\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{E5EF8507-0F59-4DE1-8676-75A1B8F27EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="7200" windowHeight="4425" xr2:uid="{C823F5A8-5044-4511-9B4E-38A6B470BD49}"/>
